--- a/dialog.xlsx
+++ b/dialog.xlsx
@@ -1,179 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="2">
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>感觉现在浑身充满了力量！</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,157 +502,160 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -678,74 +710,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +966,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="38.7272727272727" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/dialog.xlsx
+++ b/dialog.xlsx
@@ -29,9 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="4">
+  <si>
+    <t>id</t>
+  </si>
   <si>
     <t>comment</t>
+  </si>
+  <si>
+    <t>showTime</t>
   </si>
   <si>
     <t>感觉现在浑身充满了力量！</t>
@@ -968,85 +974,175 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="38.7272727272727" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7272727272727" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>1</v>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/dialog.xlsx
+++ b/dialog.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -41,6 +41,51 @@
   </si>
   <si>
     <t>感觉现在浑身充满了力量！</t>
+  </si>
+  <si>
+    <t>我又获得积分啦(★ω★)/</t>
+  </si>
+  <si>
+    <t>是打牌高手！</t>
+  </si>
+  <si>
+    <t>积分越来越多了٩(๑❛ᴗ❛๑)۶</t>
+  </si>
+  <si>
+    <t>这是什么操作？</t>
+  </si>
+  <si>
+    <t>好厉害的技艺！</t>
+  </si>
+  <si>
+    <t>枝叶在成长(～￣▽￣)～</t>
+  </si>
+  <si>
+    <t>居然要丢掉这个吗</t>
+  </si>
+  <si>
+    <t>旧的不去，新的不来吧(￣ω￣)</t>
+  </si>
+  <si>
+    <t>感觉像是喝了很烈的酒。。。</t>
+  </si>
+  <si>
+    <t>不要以为这样就赢了</t>
+  </si>
+  <si>
+    <t>好想吃松饼。。。</t>
+  </si>
+  <si>
+    <t>COS（0）=1</t>
+  </si>
+  <si>
+    <t>道德上没问题</t>
+  </si>
+  <si>
+    <t>牡蛎牡蛎</t>
+  </si>
+  <si>
+    <t>心脏要逃走了...</t>
   </si>
 </sst>
 </file>
@@ -53,13 +98,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -206,12 +257,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -526,55 +583,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
@@ -589,79 +643,88 @@
     <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -974,7 +1037,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="38.7272727272727" style="1" customWidth="1"/>
@@ -999,7 +1062,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1007,7 +1070,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -1018,10 +1081,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1029,65 +1092,65 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1095,7 +1158,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -1106,10 +1169,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1117,32 +1180,54 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" ht="17.5" spans="1:3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/dialog.xlsx
+++ b/dialog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="11430"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,16 +40,16 @@
     <t>showTime</t>
   </si>
   <si>
-    <t>感觉现在浑身充满了力量！</t>
-  </si>
-  <si>
-    <t>我又获得积分啦(★ω★)/</t>
-  </si>
-  <si>
-    <t>是打牌高手！</t>
-  </si>
-  <si>
-    <t>积分越来越多了٩(๑❛ᴗ❛๑)۶</t>
+    <t>这是给我的吗？</t>
+  </si>
+  <si>
+    <t>谢谢奈奈亲！</t>
+  </si>
+  <si>
+    <t>是手工台高手！</t>
+  </si>
+  <si>
+    <t>奈奈亲最好了！</t>
   </si>
   <si>
     <t>这是什么操作？</t>
@@ -58,7 +58,7 @@
     <t>好厉害的技艺！</t>
   </si>
   <si>
-    <t>枝叶在成长(～￣▽￣)～</t>
+    <t>物品变美观了(～￣▽￣)～</t>
   </si>
   <si>
     <t>居然要丢掉这个吗</t>
@@ -73,7 +73,7 @@
     <t>不要以为这样就赢了</t>
   </si>
   <si>
-    <t>好想吃松饼。。。</t>
+    <t>好麻烦啊</t>
   </si>
   <si>
     <t>COS（0）=1</t>
